--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E18E093-3E6C-4B4B-8DCC-1BD0B870AD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003803D0-9C8F-41F0-9856-758C71E7D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9204" yWindow="708" windowWidth="13740" windowHeight="11232" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
+    <workbookView xWindow="15984" yWindow="1404" windowWidth="12732" windowHeight="12276" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -97,7 +97,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -462,8 +462,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <f>B1/B2</f>
-        <v>59.444444444444443</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -471,7 +470,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>70</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -480,7 +479,7 @@
       </c>
       <c r="B5" s="2">
         <f>1/((2*PI()*B1)^2*B4*10^(-6))*10^12</f>
-        <v>3.1606373495607163</v>
+        <v>3160.6373495607163</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -489,7 +488,7 @@
       </c>
       <c r="B6" s="1">
         <f>1/B3</f>
-        <v>1.6822429906542057E-2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -498,7 +497,7 @@
       </c>
       <c r="B7" s="2">
         <f>B3*2*PI()*B4*10^(-6)*B1</f>
-        <v>279751.84448516311</v>
+        <v>470.61057950775108</v>
       </c>
     </row>
   </sheetData>

--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003803D0-9C8F-41F0-9856-758C71E7D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE209E24-55DD-458B-8470-3E4D4EFCF682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15984" yWindow="1404" windowWidth="12732" windowHeight="12276" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
+    <workbookView xWindow="9204" yWindow="708" windowWidth="13740" windowHeight="11232" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>f0</t>
   </si>
@@ -47,24 +47,40 @@
     <t>Q</t>
   </si>
   <si>
-    <t>C (pF)</t>
-  </si>
-  <si>
     <t>k</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>L (uH)</t>
+    <t>L (nH)</t>
+  </si>
+  <si>
+    <t>C (nF)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>r (mm)</t>
+  </si>
+  <si>
+    <t>l (mm)</t>
+  </si>
+  <si>
+    <t>wire diam (mm)</t>
+  </si>
+  <si>
+    <t>spacing (mm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -95,10 +111,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,13 +450,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC810547-319A-4F8C-B0D9-22AAD89B234B}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,8 +465,14 @@
         <f>10.7*10^6</f>
         <v>10700000</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -456,48 +480,116 @@
         <f>180*10^3</f>
         <v>180000</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <f>B1/B2</f>
+        <v>59.444444444444443</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>350</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <f>(F1/25.4)^2*F2/(9*F3/25.4+10*F3/25.4)*1000</f>
+        <v>207.21094073767094</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" s="2">
+        <f>1/((2*PI()*B1)^2*B4*10^(-9))*10^9</f>
+        <v>0.63212746991214319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <f>1/((2*PI()*B1)^2*B4*10^(-6))*10^12</f>
-        <v>3160.6373495607163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
       </c>
       <c r="B6" s="1">
         <f>1/B3</f>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.6822429906542057E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <f>B3*2*PI()*B4*10^(-9)*B1</f>
+        <v>1398.7592224258156</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <f>F10*F7+(F10-1)*F8</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <f>B3*2*PI()*B4*10^(-6)*B1</f>
-        <v>470.61057950775108</v>
+      <c r="F12">
+        <f>(F9/25.4)^2*F10/(9*F11/25.4+10*F11/25.4)*1000</f>
+        <v>436.23355944772828</v>
       </c>
     </row>
   </sheetData>

--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE209E24-55DD-458B-8470-3E4D4EFCF682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A4E34D-C78A-4C1B-B8C8-371ED1A40F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9204" yWindow="708" windowWidth="13740" windowHeight="11232" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
+    <workbookView xWindow="15984" yWindow="1404" windowWidth="12732" windowHeight="12276" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B5" s="2">
         <f>1/((2*PI()*B1)^2*B4*10^(-9))*10^9</f>
-        <v>0.63212746991214319</v>
+        <v>0.55311153617312536</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -541,13 +541,13 @@
       </c>
       <c r="B7" s="2">
         <f>B3*2*PI()*B4*10^(-9)*B1</f>
-        <v>1398.7592224258156</v>
+        <v>1598.5819684866462</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -555,7 +555,8 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <f>F7</f>
+        <v>1.31</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -580,7 +581,7 @@
       </c>
       <c r="F11">
         <f>F10*F7+(F10-1)*F8</f>
-        <v>19</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -589,7 +590,7 @@
       </c>
       <c r="F12">
         <f>(F9/25.4)^2*F10/(9*F11/25.4+10*F11/25.4)*1000</f>
-        <v>436.23355944772828</v>
+        <v>333.00271713567042</v>
       </c>
     </row>
   </sheetData>

--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A4E34D-C78A-4C1B-B8C8-371ED1A40F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43198EA-FE4B-436B-8F4A-ED43398472BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15984" yWindow="1404" windowWidth="12732" windowHeight="12276" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
@@ -555,8 +555,7 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <f>F7</f>
-        <v>1.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -581,7 +580,7 @@
       </c>
       <c r="F11">
         <f>F10*F7+(F10-1)*F8</f>
-        <v>24.89</v>
+        <v>13.100000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -590,7 +589,7 @@
       </c>
       <c r="F12">
         <f>(F9/25.4)^2*F10/(9*F11/25.4+10*F11/25.4)*1000</f>
-        <v>333.00271713567042</v>
+        <v>632.70516255777375</v>
       </c>
     </row>
   </sheetData>

--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43198EA-FE4B-436B-8F4A-ED43398472BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB267D86-72CF-493E-9528-503C1D35D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15984" yWindow="1404" windowWidth="12732" windowHeight="12276" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>f0</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>spacing (mm)</t>
+  </si>
+  <si>
+    <t>f (kHz)</t>
   </si>
 </sst>
 </file>
@@ -492,8 +495,8 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <f>B1/B2</f>
-        <v>59.444444444444443</v>
+        <f>150</f>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -506,8 +509,8 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>400</v>
+      <c r="B4" s="3">
+        <v>320</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -523,7 +526,7 @@
       </c>
       <c r="B5" s="2">
         <f>1/((2*PI()*B1)^2*B4*10^(-9))*10^9</f>
-        <v>0.55311153617312536</v>
+        <v>0.69138942021640659</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -532,7 +535,7 @@
       </c>
       <c r="B6" s="1">
         <f>1/B3</f>
-        <v>1.6822429906542057E-2</v>
+        <v>6.6666666666666671E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -541,7 +544,7 @@
       </c>
       <c r="B7" s="2">
         <f>B3*2*PI()*B4*10^(-9)*B1</f>
-        <v>1598.5819684866462</v>
+        <v>3227.0439737674355</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -555,7 +558,7 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -563,33 +566,52 @@
         <v>8</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>15000</v>
+      </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>10000</v>
+      </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11">
-        <f>F10*F7+(F10-1)*F8</f>
-        <v>13.100000000000001</v>
+        <f>F7*F10+(F10-1)*F8</f>
+        <v>12.86</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2">
+        <f>1/(2*PI()*B11*B10)*1000000000</f>
+        <v>1.0610329539459691</v>
+      </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
-      <c r="F12">
-        <f>(F9/25.4)^2*F10/(9*F11/25.4+10*F11/25.4)*1000</f>
-        <v>632.70516255777375</v>
+      <c r="F12" s="3">
+        <f>(F9/25.4)^2*F10^2/(9*F11/25.4+10*F11/25.4)*1000</f>
+        <v>145.01543286462197</v>
       </c>
     </row>
   </sheetData>

--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB267D86-72CF-493E-9528-503C1D35D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6A234-9053-4D07-A775-59EC0DAD8050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
+    <workbookView xWindow="6840" yWindow="732" windowWidth="16200" windowHeight="11232" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -526,7 +526,7 @@
       </c>
       <c r="B5" s="2">
         <f>1/((2*PI()*B1)^2*B4*10^(-9))*10^9</f>
-        <v>0.69138942021640659</v>
+        <v>0.73748204823083374</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B7" s="2">
         <f>B3*2*PI()*B4*10^(-9)*B1</f>
-        <v>3227.0439737674355</v>
+        <v>3025.3537254069711</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>

--- a/lab4/calculator.xlsx
+++ b/lab4/calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6A234-9053-4D07-A775-59EC0DAD8050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A266CF-9AD1-41DA-A406-6E0C827CB601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6840" yWindow="732" windowWidth="16200" windowHeight="11232" xr2:uid="{8EEEAC13-49F3-4E7C-B747-C8BB4ADA5146}"/>
   </bookViews>
@@ -492,11 +492,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
-        <f>150</f>
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -507,10 +506,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="2">
+        <f>1/((2*PI()*B1)^2*B3*10^(-9))*10^9</f>
+        <v>0.55311153617312536</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -522,29 +522,28 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
-        <f>1/((2*PI()*B1)^2*B4*10^(-9))*10^9</f>
-        <v>0.73748204823083374</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1">
-        <f>1/B3</f>
-        <v>6.6666666666666671E-3</v>
+        <v>2</v>
+      </c>
+      <c r="B6" s="3">
+        <f>B5*SQRT(B4/B3)</f>
+        <v>148.74293746906108</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2">
-        <f>B3*2*PI()*B4*10^(-9)*B1</f>
-        <v>3025.3537254069711</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <f>1/B6</f>
+        <v>6.7230082786821571E-3</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -566,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -580,7 +579,7 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -595,7 +594,7 @@
       </c>
       <c r="F11">
         <f>F7*F10+(F10-1)*F8</f>
-        <v>12.86</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -611,7 +610,7 @@
       </c>
       <c r="F12" s="3">
         <f>(F9/25.4)^2*F10^2/(9*F11/25.4+10*F11/25.4)*1000</f>
-        <v>145.01543286462197</v>
+        <v>325.90458640293878</v>
       </c>
     </row>
   </sheetData>
